--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484697_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484697_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5763</v>
+        <v>6.4256</v>
       </c>
       <c r="E2" t="n">
-        <v>4.3549</v>
+        <v>4.0804</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2213</v>
+        <v>2.3452</v>
       </c>
       <c r="G2" t="n">
         <v>1.5993</v>
@@ -610,13 +610,13 @@
         <v>2.0158</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6942</v>
+        <v>1.5436</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3175</v>
+        <v>1.043</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3767</v>
+        <v>0.5004999999999999</v>
       </c>
       <c r="V2" t="n">
         <v>1.267</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2633</v>
+        <v>5.3235</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1542</v>
+        <v>2.5117</v>
       </c>
       <c r="F3" t="n">
-        <v>3.1091</v>
+        <v>2.8118</v>
       </c>
       <c r="G3" t="n">
         <v>1.2987</v>
@@ -688,13 +688,13 @@
         <v>2.5656</v>
       </c>
       <c r="S3" t="n">
-        <v>1.3599</v>
+        <v>1.4201</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2911</v>
+        <v>0.6486</v>
       </c>
       <c r="U3" t="n">
-        <v>1.0687</v>
+        <v>0.7715</v>
       </c>
       <c r="V3" t="n">
         <v>0.9554</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. COMPANY LOPEZ</t>
+          <t>L. BARCOS PERALTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9748</v>
+        <v>4.1999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0553</v>
+        <v>2.8641</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9196</v>
+        <v>1.3358</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7318</v>
+        <v>0.9469</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3901</v>
+        <v>-0.22</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.1219</v>
+        <v>1.1669</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.272</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6253</v>
+        <v>0.2227</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.8973</v>
+        <v>0.7183</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4597</v>
+        <v>0.0059</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.2351</v>
+        <v>-0.4427</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2246</v>
+        <v>0.4486</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.6493</v>
+        <v>1.0995</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1673</v>
+        <v>1.1772</v>
       </c>
       <c r="T4" t="n">
-        <v>1.7934</v>
+        <v>0.9468</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3739</v>
+        <v>0.2304</v>
       </c>
       <c r="V4" t="n">
-        <v>1.89</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>2.5339</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. BARCOS PERALTA</t>
+          <t>A. COMPANY LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.6752</v>
+        <v>3.8555</v>
       </c>
       <c r="E5" t="n">
-        <v>3.2898</v>
+        <v>2.6296</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3853</v>
+        <v>1.2259</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9469</v>
+        <v>-1.7318</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.22</v>
+        <v>0.3901</v>
       </c>
       <c r="I5" t="n">
-        <v>1.1669</v>
+        <v>-2.1219</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9409999999999999</v>
+        <v>-1.272</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2227</v>
+        <v>0.6253</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7183</v>
+        <v>-1.8973</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0059</v>
+        <v>-0.4597</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4427</v>
+        <v>-0.2351</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4486</v>
+        <v>-0.2246</v>
       </c>
       <c r="P5" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.0995</v>
+        <v>1.6493</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6525</v>
+        <v>2.0479</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3726</v>
+        <v>1.3677</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2799</v>
+        <v>0.6802</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9762999999999999</v>
+        <v>1.89</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9762999999999999</v>
+        <v>2.5339</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.6439</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.9862</v>
+        <v>3.064</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3303</v>
+        <v>3.1108</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3441</v>
+        <v>-0.0468</v>
       </c>
       <c r="G6" t="n">
         <v>2.4072</v>
@@ -922,13 +922,13 @@
         <v>2.0158</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.8243</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0423</v>
+        <v>0.8228</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2958</v>
+        <v>0.0015</v>
       </c>
       <c r="V6" t="n">
         <v>-1.267</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.4703</v>
+        <v>2.6522</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4199</v>
+        <v>2.3788</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0504</v>
+        <v>0.2734</v>
       </c>
       <c r="G7" t="n">
         <v>0.0978</v>
@@ -1000,13 +1000,13 @@
         <v>1.6493</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6683</v>
+        <v>1.8501</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3726</v>
+        <v>1.3315</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2957</v>
+        <v>0.5187</v>
       </c>
       <c r="V7" t="n">
         <v>-0.945</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0281</v>
+        <v>1.588</v>
       </c>
       <c r="E8" t="n">
-        <v>2.784</v>
+        <v>2.5917</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.7559</v>
+        <v>-1.0037</v>
       </c>
       <c r="G8" t="n">
         <v>1.8024</v>
@@ -1078,13 +1078,13 @@
         <v>0.733</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6863</v>
+        <v>1.2462</v>
       </c>
       <c r="T8" t="n">
-        <v>1.3726</v>
+        <v>1.1803</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3137</v>
+        <v>0.066</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2774</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. MARTÍNEZ TEJERO</t>
+          <t>J. ARNAIZ VEGA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3251</v>
+        <v>0.6051</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3251</v>
+        <v>0.3911</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.214</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3251</v>
+        <v>-0.2484</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3251</v>
+        <v>-1.2839</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1.0355</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3251</v>
+        <v>1.1333</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3251</v>
+        <v>-0.3192</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.4525</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>-1.3818</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>-0.9647</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.417</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.733</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9163</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.6493</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.1101</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>0.1637</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-0.0536</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.0104</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. ARNAIZ VEGA</t>
+          <t>J. MARTÍNEZ TEJERO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3733</v>
+        <v>0.3251</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4882</v>
+        <v>0.3251</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1149</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.2484</v>
+        <v>0.3251</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2839</v>
+        <v>0.3251</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0355</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.1333</v>
+        <v>0.3251</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.3192</v>
+        <v>0.3251</v>
       </c>
       <c r="L11" t="n">
-        <v>1.4525</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3818</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9647</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.417</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0.733</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9163</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.6493</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8683</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7157</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1527</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0104</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. MARTINEZ TEJERO</t>
+          <t>P. BUSTAMANTE CONTRERAS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,64 +1345,64 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.5071</v>
+        <v>-0.2001</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3648</v>
+        <v>-0.7956</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.872</v>
+        <v>0.5955</v>
       </c>
       <c r="G12" t="n">
-        <v>0.2459</v>
+        <v>-1.4824</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0074</v>
+        <v>1.223</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2532</v>
+        <v>-2.7053</v>
       </c>
       <c r="J12" t="n">
-        <v>2.5572</v>
+        <v>-1.2394</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2138</v>
+        <v>1.2414</v>
       </c>
       <c r="L12" t="n">
-        <v>1.3434</v>
+        <v>-2.4808</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3113</v>
+        <v>-0.243</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2211</v>
+        <v>-0.0184</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.0902</v>
+        <v>-0.2246</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>0.1833</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9163</v>
+        <v>1.0995</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1195</v>
+        <v>1.099</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0355</v>
+        <v>1.0381</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.155</v>
+        <v>0.0609</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6335</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3115</v>
+        <v>0.3219</v>
       </c>
       <c r="X12" t="n">
         <v>-0.3219</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. BUSTAMANTE CONTRERAS</t>
+          <t>J. MARTINEZ TEJERO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,64 +1423,64 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-1.7891</v>
+        <v>-0.3833</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.9634</v>
+        <v>1.3648</v>
       </c>
       <c r="F13" t="n">
-        <v>0.1743</v>
+        <v>-1.7481</v>
       </c>
       <c r="G13" t="n">
-        <v>-1.4824</v>
+        <v>0.2459</v>
       </c>
       <c r="H13" t="n">
-        <v>1.223</v>
+        <v>-0.0074</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.7053</v>
+        <v>0.2532</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.2394</v>
+        <v>2.5572</v>
       </c>
       <c r="K13" t="n">
-        <v>1.2414</v>
+        <v>1.2138</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.4808</v>
+        <v>1.3434</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.243</v>
+        <v>-2.3113</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0184</v>
+        <v>-1.2211</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.2246</v>
+        <v>-1.0902</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1833</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-0.9163</v>
       </c>
       <c r="R13" t="n">
-        <v>1.0995</v>
+        <v>0.9163</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.49</v>
+        <v>0.0043</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1297</v>
+        <v>0.0355</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3603</v>
+        <v>-0.0311</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.6335</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3219</v>
+        <v>-0.3115</v>
       </c>
       <c r="X13" t="n">
         <v>-0.3219</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>28.1941</v>
+        <v>29.0198</v>
       </c>
       <c r="E14" t="n">
-        <v>23.1387</v>
+        <v>23.9645</v>
       </c>
       <c r="F14" t="n">
-        <v>5.0552</v>
+        <v>5.055300000000001</v>
       </c>
       <c r="G14" t="n">
         <v>4.869599999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>3.5874</v>
+        <v>3.587399999999999</v>
       </c>
       <c r="I14" t="n">
         <v>1.282</v>
@@ -1546,13 +1546,13 @@
         <v>16.4929</v>
       </c>
       <c r="S14" t="n">
-        <v>10.9919</v>
+        <v>11.8175</v>
       </c>
       <c r="T14" t="n">
-        <v>8.318600000000002</v>
+        <v>9.144400000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>2.6731</v>
+        <v>2.6733</v>
       </c>
       <c r="V14" t="n">
         <v>2.2536</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.407</v>
+        <v>2.3633</v>
       </c>
       <c r="E15" t="n">
-        <v>6.7546</v>
+        <v>6.5623</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.3477</v>
+        <v>-4.199</v>
       </c>
       <c r="G15" t="n">
         <v>2.2163</v>
@@ -1624,13 +1624,13 @@
         <v>0.733</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5977</v>
+        <v>-0.6414</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3092</v>
+        <v>0.1169</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.907</v>
+        <v>-0.7583</v>
       </c>
       <c r="V15" t="n">
         <v>1.888</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.5303</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8037</v>
+        <v>1.5153</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8859</v>
+        <v>-0.985</v>
       </c>
       <c r="G17" t="n">
         <v>1.5148</v>
@@ -1780,13 +1780,13 @@
         <v>0.3665</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0472</v>
+        <v>-0.4348</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2557</v>
+        <v>-0.0328</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3029</v>
+        <v>-0.402</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9199000000000001</v>
+        <v>-0.8355</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7627</v>
+        <v>-0.2819</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1573</v>
+        <v>-0.5536</v>
       </c>
       <c r="G18" t="n">
         <v>1.178</v>
@@ -1858,13 +1858,13 @@
         <v>0.733</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.3435</v>
+        <v>-1.2591</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9909</v>
+        <v>-0.5102</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3525</v>
+        <v>-0.7489</v>
       </c>
       <c r="V18" t="n">
         <v>-0.5712</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5942</v>
+        <v>-1.5694</v>
       </c>
       <c r="E19" t="n">
         <v>-1.7008</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1066</v>
+        <v>0.1313</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5003</v>
@@ -1936,13 +1936,13 @@
         <v>0.3665</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6064000000000001</v>
+        <v>-0.5816</v>
       </c>
       <c r="T19" t="n">
         <v>-0.1652</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4413</v>
+        <v>-0.4165</v>
       </c>
       <c r="V19" t="n">
         <v>0.0623</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. ARIJA DE LA PENA</t>
+          <t>M. PERAL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2622</v>
+        <v>-2.2126</v>
       </c>
       <c r="E20" t="n">
-        <v>0.0335</v>
+        <v>1.8275</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2957</v>
+        <v>-4.0401</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.9287</v>
+        <v>2.4715</v>
       </c>
       <c r="H20" t="n">
-        <v>0.4049</v>
+        <v>2.9487</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3336</v>
+        <v>-0.4772</v>
       </c>
       <c r="J20" t="n">
-        <v>0.9520999999999999</v>
+        <v>4.7252</v>
       </c>
       <c r="K20" t="n">
-        <v>1.9008</v>
+        <v>4.5608</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9487</v>
+        <v>0.1644</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8808</v>
+        <v>-2.2537</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4959</v>
+        <v>-1.6121</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3849</v>
+        <v>-0.6415999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4661</v>
+        <v>-3.2986</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.8326</v>
+        <v>-4.5814</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3665</v>
+        <v>1.2828</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0901</v>
+        <v>-2.7023</v>
       </c>
       <c r="T20" t="n">
-        <v>1.2255</v>
+        <v>-0.8502999999999999</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1354</v>
+        <v>-1.852</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9575</v>
+        <v>1.3168</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3115</v>
+        <v>2.5339</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.646</v>
+        <v>-1.2172</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.1528</v>
+        <v>-2.57</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4929</v>
+        <v>-1.1083</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.6599</v>
+        <v>-1.4617</v>
       </c>
       <c r="G21" t="n">
         <v>-0.8106</v>
@@ -2092,13 +2092,13 @@
         <v>0.1833</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6092</v>
+        <v>-1.0264</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7157</v>
+        <v>-0.3311</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.8935</v>
+        <v>-0.6953</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. PERAL</t>
+          <t>D. ARIJA DE LA PENA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.3564</v>
+        <v>-3.3476</v>
       </c>
       <c r="E22" t="n">
-        <v>1.1544</v>
+        <v>-0.928</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.5108</v>
+        <v>-2.4196</v>
       </c>
       <c r="G22" t="n">
-        <v>2.4715</v>
+        <v>-0.9287</v>
       </c>
       <c r="H22" t="n">
-        <v>2.9487</v>
+        <v>0.4049</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4772</v>
+        <v>-1.3336</v>
       </c>
       <c r="J22" t="n">
-        <v>4.7252</v>
+        <v>0.9520999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>4.5608</v>
+        <v>1.9008</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1644</v>
+        <v>-0.9487</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.2537</v>
+        <v>-1.8808</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.6121</v>
+        <v>-1.4959</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.3849</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.2986</v>
+        <v>-1.4661</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.5814</v>
+        <v>-1.8326</v>
       </c>
       <c r="R22" t="n">
-        <v>1.2828</v>
+        <v>0.3665</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.8461</v>
+        <v>0.0047</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.5233</v>
+        <v>0.264</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.3227</v>
+        <v>-0.2593</v>
       </c>
       <c r="V22" t="n">
-        <v>1.3168</v>
+        <v>-0.9575</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5339</v>
+        <v>-0.3115</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.2172</v>
+        <v>-0.646</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.5596</v>
+        <v>-3.5101</v>
       </c>
       <c r="E23" t="n">
         <v>-2.7272</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8324</v>
+        <v>-0.7829</v>
       </c>
       <c r="G23" t="n">
         <v>-1.6391</v>
@@ -2248,13 +2248,13 @@
         <v>0.5498</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.7</v>
+        <v>-0.6505</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2753</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4247</v>
+        <v>-0.3752</v>
       </c>
       <c r="V23" t="n">
         <v>0.0623</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.1014</v>
+        <v>-3.5711</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6244</v>
+        <v>-0.1436</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.4771</v>
+        <v>-3.4275</v>
       </c>
       <c r="G24" t="n">
         <v>-1.2719</v>
@@ -2326,13 +2326,13 @@
         <v>0.5498</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.1103</v>
+        <v>-1.5799</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7526</v>
+        <v>-0.2719</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3576</v>
+        <v>-1.3081</v>
       </c>
       <c r="V24" t="n">
         <v>-1.2691</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.6962</v>
+        <v>-5.3941</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.1531</v>
+        <v>-2.8262</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.5431</v>
+        <v>-2.5679</v>
       </c>
       <c r="G25" t="n">
         <v>-2.9678</v>
@@ -2404,13 +2404,13 @@
         <v>0.733</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9328</v>
+        <v>-1.6307</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0709</v>
+        <v>-0.6022</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.0037</v>
+        <v>-1.0285</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5287</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-9.4513</v>
+        <v>-9.6525</v>
       </c>
       <c r="E26" t="n">
-        <v>-5.649</v>
+        <v>-5.5528</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.8024</v>
+        <v>-4.0997</v>
       </c>
       <c r="G26" t="n">
         <v>-5.707</v>
@@ -2482,13 +2482,13 @@
         <v>0.5498</v>
       </c>
       <c r="S26" t="n">
-        <v>-0.2887</v>
+        <v>-0.4898</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.1116</v>
+        <v>-0.0154</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.1771</v>
+        <v>-0.4744</v>
       </c>
       <c r="V26" t="n">
         <v>-1.2566</v>
@@ -2515,19 +2515,19 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-28.1939</v>
+        <v>-28.194</v>
       </c>
       <c r="E27" t="n">
-        <v>-3.788599999999998</v>
+        <v>-3.788400000000002</v>
       </c>
       <c r="F27" t="n">
         <v>-24.4057</v>
       </c>
       <c r="G27" t="n">
-        <v>-4.869499999999999</v>
+        <v>-4.8695</v>
       </c>
       <c r="H27" t="n">
-        <v>-3.587499999999999</v>
+        <v>-3.5875</v>
       </c>
       <c r="I27" t="n">
         <v>-1.2821</v>
@@ -2563,10 +2563,10 @@
         <v>-10.9918</v>
       </c>
       <c r="T27" t="n">
-        <v>-2.6733</v>
+        <v>-2.6735</v>
       </c>
       <c r="U27" t="n">
-        <v>-8.318399999999999</v>
+        <v>-8.3185</v>
       </c>
       <c r="V27" t="n">
         <v>-2.2537</v>
